--- a/Vplan_TestCase_Checklist.xlsx
+++ b/Vplan_TestCase_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83377f57b735e897/Máy tính/AXI2AHB1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5287F0E0-9CFB-4940-8E4B-14AC06EFB685}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFBF774D-6AB0-4138-B9C8-9C4D02865822}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,9 +88,6 @@
     <t>axi4_blocking_wrap_burst_write_test</t>
   </si>
   <si>
-    <t>Blocking WRAP burst write transaction.</t>
-  </si>
-  <si>
     <t>Verify AXI4 WRAP burst writes are correctly unrolled into AHB-Lite single/INCR accesses with proper address wrapping.</t>
   </si>
   <si>
@@ -506,6 +503,9 @@
   </si>
   <si>
     <t>Completed</t>
+  </si>
+  <si>
+    <t>Blocking WRAP burst write transaction with the different sizes(2,4,8,16) .</t>
   </si>
 </sst>
 </file>
@@ -983,13 +983,13 @@
         <v>15</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="F4" s="9">
         <v>46240</v>
@@ -1000,21 +1000,21 @@
       <c r="H4" s="3"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="F5" s="9">
         <v>46240</v>
@@ -1026,220 +1026,220 @@
       <c r="I5" s="6"/>
     </row>
     <row r="6" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="9">
+        <v>46240</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="6"/>
+    </row>
+    <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F7" s="9">
+        <v>46240</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="4"/>
-    </row>
-    <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="C8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F8" s="9">
+        <v>46240</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F9" s="9">
+        <v>46240</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="4"/>
-    </row>
-    <row r="9" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="s">
+      <c r="C10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="E10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="F10" s="9">
+        <v>46240</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="6"/>
-    </row>
-    <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F11" s="9">
+        <v>46240</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <v>10</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="4"/>
-    </row>
-    <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="5">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="C12" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="E12" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="F12" s="9">
+        <v>46240</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="6"/>
+    </row>
+    <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="6"/>
-    </row>
-    <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="5">
-        <v>12</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="F13" s="9">
         <v>46240</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="6"/>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="F14" s="9">
         <v>46240</v>
@@ -1255,16 +1255,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="D15" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="E15" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="F15" s="9">
         <v>46240</v>
@@ -1280,16 +1280,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="F16" s="9">
         <v>46240</v>
@@ -1305,16 +1305,16 @@
         <v>18</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="D17" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="E17" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="F17" s="9">
         <v>46240</v>
@@ -1330,16 +1330,16 @@
         <v>19</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="F18" s="9">
         <v>46240</v>
@@ -1355,16 +1355,16 @@
         <v>20</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="D19" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="E19" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="F19" s="9">
         <v>46240</v>
@@ -1380,16 +1380,16 @@
         <v>21</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="F20" s="9">
         <v>46240</v>
@@ -1405,16 +1405,16 @@
         <v>22</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="D21" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="E21" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>86</v>
       </c>
       <c r="F21" s="10">
         <v>46240</v>
@@ -1430,16 +1430,16 @@
         <v>23</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="E22" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="F22" s="11">
         <v>46240</v>
@@ -1455,16 +1455,16 @@
         <v>24</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="E23" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>94</v>
       </c>
       <c r="F23" s="10">
         <v>46240</v>
@@ -1480,16 +1480,16 @@
         <v>25</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="F24" s="11">
         <v>46240</v>
@@ -1505,16 +1505,16 @@
         <v>26</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="D25" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="E25" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="F25" s="11">
         <v>46240</v>
@@ -1530,16 +1530,16 @@
         <v>27</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>106</v>
       </c>
       <c r="F26" s="11">
         <v>46240</v>
@@ -1556,11 +1556,11 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="G3:G26" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G14:G26 G3:G13" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Not Started,In Progress,Completed,Blocked"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H3:H26" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H14:H26 H3:H13" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Pass,Fail,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1588,7 +1588,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1601,22 +1601,22 @@
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>7</v>
@@ -1630,16 +1630,16 @@
     </row>
     <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>116</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -1651,16 +1651,16 @@
     </row>
     <row r="4" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -1672,16 +1672,16 @@
     </row>
     <row r="5" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -1693,16 +1693,16 @@
     </row>
     <row r="6" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="7" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -1735,16 +1735,16 @@
     </row>
     <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>131</v>
-      </c>
       <c r="D8" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -1756,16 +1756,16 @@
     </row>
     <row r="9" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>135</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -1777,16 +1777,16 @@
     </row>
     <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C10" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -1798,16 +1798,16 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>140</v>
-      </c>
       <c r="D11" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1819,16 +1819,16 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>143</v>
-      </c>
       <c r="D12" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -1840,16 +1840,16 @@
     </row>
     <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>147</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1861,16 +1861,16 @@
     </row>
     <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>150</v>
-      </c>
       <c r="D14" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -1882,12 +1882,12 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C17" s="8">
         <f>COUNTA(A3:A14)</f>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C18" s="8">
         <f>COUNTIF(H3:H14,"Pass")</f>
@@ -1905,7 +1905,7 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C19" s="8">
         <f>COUNTIF(H3:H14,"Fail")</f>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C20" s="8">
         <f>COUNTIF(G3:G14,"Completed")</f>

--- a/Vplan_TestCase_Checklist.xlsx
+++ b/Vplan_TestCase_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83377f57b735e897/Máy tính/AXI2AHB1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFBF774D-6AB0-4138-B9C8-9C4D02865822}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78591B60-14AF-4D7E-9876-3C7C47DA7720}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="158">
   <si>
     <t>AXI4-to-AHB-Lite Bridge - Verification Test Cases</t>
   </si>
@@ -506,13 +506,19 @@
   </si>
   <si>
     <t>Blocking WRAP burst write transaction with the different sizes(2,4,8,16) .</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -545,8 +551,36 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -568,6 +602,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
@@ -599,11 +663,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -624,10 +685,23 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -713,6 +787,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -904,651 +982,663 @@
     <col min="5" max="5" width="46" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="8" max="8" width="10" style="13" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="6"/>
+      <c r="F3" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="4"/>
+      <c r="F4" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="I4" s="3"/>
     </row>
     <row r="5" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>12</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F5" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="6"/>
+      <c r="F5" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="6"/>
+      <c r="F6" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="11"/>
+      <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="4"/>
+      <c r="F7" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="I7" s="3"/>
     </row>
     <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
+      <c r="A8" s="4">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="6"/>
+      <c r="F8" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="11"/>
+      <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="4"/>
+      <c r="F9" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="12"/>
+      <c r="I9" s="3"/>
     </row>
     <row r="10" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
+      <c r="A10" s="4">
         <v>8</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="6"/>
+      <c r="F10" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="11"/>
+      <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>9</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="4"/>
+      <c r="F11" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="5">
-        <v>10</v>
-      </c>
-      <c r="B12" s="6" t="s">
+      <c r="A12" s="4">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="6"/>
+      <c r="F12" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="11"/>
+      <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="4"/>
+      <c r="F13" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="12"/>
+      <c r="I13" s="3"/>
     </row>
     <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F14" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="4"/>
+      <c r="F14" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="12"/>
+      <c r="I14" s="3"/>
     </row>
     <row r="15" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="5">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="6"/>
+      <c r="F15" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="4"/>
+      <c r="F16" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="I16" s="3"/>
     </row>
     <row r="17" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="5">
+      <c r="A17" s="4">
         <v>18</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H17" s="5"/>
-      <c r="I17" s="6"/>
+      <c r="F17" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
+      <c r="A18" s="2">
         <v>19</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F18" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="4"/>
+      <c r="F18" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="12"/>
+      <c r="I18" s="3"/>
     </row>
     <row r="19" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="5">
+      <c r="A19" s="4">
         <v>20</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F19" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H19" s="5"/>
-      <c r="I19" s="6"/>
+      <c r="F19" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="11"/>
+      <c r="I19" s="5"/>
     </row>
     <row r="20" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
+      <c r="A20" s="2">
         <v>21</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F20" s="9">
-        <v>46240</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="4"/>
+      <c r="F20" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="12"/>
+      <c r="I20" s="3"/>
     </row>
     <row r="21" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="5">
+      <c r="A21" s="4">
         <v>22</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F21" s="10">
-        <v>46240</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="6"/>
+      <c r="F21" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="11"/>
+      <c r="I21" s="5"/>
     </row>
     <row r="22" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
+      <c r="A22" s="2">
         <v>23</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="F22" s="11">
-        <v>46240</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="4"/>
+      <c r="F22" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="12"/>
+      <c r="I22" s="3"/>
     </row>
     <row r="23" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
+      <c r="A23" s="4">
         <v>24</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="F23" s="10">
-        <v>46240</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H23" s="5"/>
-      <c r="I23" s="6"/>
+      <c r="F23" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="5"/>
     </row>
     <row r="24" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
+      <c r="A24" s="2">
         <v>25</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F24" s="11">
-        <v>46240</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="4"/>
+      <c r="F24" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="12"/>
+      <c r="I24" s="3"/>
     </row>
     <row r="25" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="5">
+      <c r="A25" s="4">
         <v>26</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F25" s="11">
-        <v>46240</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H25" s="5"/>
-      <c r="I25" s="6"/>
+      <c r="F25" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" s="11"/>
+      <c r="I25" s="5"/>
     </row>
     <row r="26" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
+      <c r="A26" s="2">
         <v>27</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F26" s="11">
-        <v>46240</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="4"/>
+      <c r="F26" s="8">
+        <v>46240</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="12"/>
+      <c r="I26" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:I26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1587,336 +1677,336 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="4"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="3"/>
     </row>
     <row r="4" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="6"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="4"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="6"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="4"/>
+      <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="4"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="3"/>
     </row>
     <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="6"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="4"/>
+      <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="4"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="3"/>
     </row>
     <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="6"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="4"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="6"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="4"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="3"/>
     </row>
     <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="6"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="4"/>
+      <c r="I14" s="5"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <f>COUNTA(A3:A14)</f>
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <f>COUNTIF(H3:H14,"Pass")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <f>COUNTIF(H3:H14,"Fail")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="7">
         <f>COUNTIF(G3:G14,"Completed")</f>
         <v>0</v>
       </c>

--- a/Vplan_TestCase_Checklist.xlsx
+++ b/Vplan_TestCase_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83377f57b735e897/Máy tính/AXI2AHB1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78591B60-14AF-4D7E-9876-3C7C47DA7720}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE14D151-1B76-4034-B7CF-21A6017D1763}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="158">
   <si>
     <t>AXI4-to-AHB-Lite Bridge - Verification Test Cases</t>
   </si>
@@ -685,9 +685,6 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -702,6 +699,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -982,22 +982,22 @@
     <col min="5" max="5" width="46" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="10" style="13" customWidth="1"/>
+    <col min="8" max="8" width="10" style="12" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1021,7 +1021,7 @@
       <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="9" t="s">
         <v>8</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -1050,7 +1050,7 @@
       <c r="G3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="10" t="s">
         <v>157</v>
       </c>
       <c r="I3" s="5"/>
@@ -1077,7 +1077,7 @@
       <c r="G4" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="13" t="s">
         <v>156</v>
       </c>
       <c r="I4" s="3"/>
@@ -1104,7 +1104,7 @@
       <c r="G5" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>156</v>
       </c>
       <c r="I5" s="5"/>
@@ -1129,9 +1129,11 @@
         <v>46240</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="11"/>
+        <v>154</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>156</v>
+      </c>
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1156,7 +1158,7 @@
       <c r="G7" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="13" t="s">
         <v>156</v>
       </c>
       <c r="I7" s="3"/>
@@ -1183,7 +1185,7 @@
       <c r="G8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="11"/>
+      <c r="H8" s="10"/>
       <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1208,7 +1210,7 @@
       <c r="G9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="12"/>
+      <c r="H9" s="11"/>
       <c r="I9" s="3"/>
     </row>
     <row r="10" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
@@ -1233,7 +1235,7 @@
       <c r="G10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="11"/>
+      <c r="H10" s="10"/>
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1258,7 +1260,7 @@
       <c r="G11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="12"/>
+      <c r="H11" s="11"/>
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1283,7 +1285,7 @@
       <c r="G12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="11"/>
+      <c r="H12" s="10"/>
       <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1308,7 +1310,7 @@
       <c r="G13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="12"/>
+      <c r="H13" s="11"/>
       <c r="I13" s="3"/>
     </row>
     <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1331,9 +1333,11 @@
         <v>46240</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="12"/>
+        <v>154</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>156</v>
+      </c>
       <c r="I14" s="3"/>
     </row>
     <row r="15" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1358,7 +1362,7 @@
       <c r="G15" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="14" t="s">
         <v>156</v>
       </c>
       <c r="I15" s="5"/>
@@ -1385,7 +1389,7 @@
       <c r="G16" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="13" t="s">
         <v>156</v>
       </c>
       <c r="I16" s="3"/>
@@ -1412,7 +1416,7 @@
       <c r="G17" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H17" s="11"/>
+      <c r="H17" s="10"/>
       <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1437,7 +1441,7 @@
       <c r="G18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H18" s="12"/>
+      <c r="H18" s="11"/>
       <c r="I18" s="3"/>
     </row>
     <row r="19" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1462,7 +1466,7 @@
       <c r="G19" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="11"/>
+      <c r="H19" s="10"/>
       <c r="I19" s="5"/>
     </row>
     <row r="20" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1487,7 +1491,7 @@
       <c r="G20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H20" s="12"/>
+      <c r="H20" s="11"/>
       <c r="I20" s="3"/>
     </row>
     <row r="21" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1512,7 +1516,7 @@
       <c r="G21" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="11"/>
+      <c r="H21" s="10"/>
       <c r="I21" s="5"/>
     </row>
     <row r="22" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1537,7 +1541,7 @@
       <c r="G22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="12"/>
+      <c r="H22" s="11"/>
       <c r="I22" s="3"/>
     </row>
     <row r="23" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1562,7 +1566,7 @@
       <c r="G23" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H23" s="11"/>
+      <c r="H23" s="10"/>
       <c r="I23" s="5"/>
     </row>
     <row r="24" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1587,7 +1591,7 @@
       <c r="G24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="12"/>
+      <c r="H24" s="11"/>
       <c r="I24" s="3"/>
     </row>
     <row r="25" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1612,7 +1616,7 @@
       <c r="G25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H25" s="11"/>
+      <c r="H25" s="10"/>
       <c r="I25" s="5"/>
     </row>
     <row r="26" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1637,7 +1641,7 @@
       <c r="G26" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H26" s="12"/>
+      <c r="H26" s="11"/>
       <c r="I26" s="3"/>
     </row>
   </sheetData>
@@ -1646,11 +1650,11 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="G14:G26 G3:G13" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G3:G26" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Not Started,In Progress,Completed,Blocked"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H14:H26 H3:H13" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H3:H26" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Pass,Fail,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1677,17 +1681,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">

--- a/Vplan_TestCase_Checklist.xlsx
+++ b/Vplan_TestCase_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83377f57b735e897/Máy tính/AXI2AHB1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE14D151-1B76-4034-B7CF-21A6017D1763}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D43DF1A-4BDD-4587-B4B1-9169136FAD74}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="158">
   <si>
     <t>AXI4-to-AHB-Lite Bridge - Verification Test Cases</t>
   </si>
@@ -663,7 +663,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -702,6 +702,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1441,7 +1444,9 @@
       <c r="G18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H18" s="11"/>
+      <c r="H18" s="13" t="s">
+        <v>156</v>
+      </c>
       <c r="I18" s="3"/>
     </row>
     <row r="19" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1466,7 +1471,9 @@
       <c r="G19" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="10"/>
+      <c r="H19" s="13" t="s">
+        <v>156</v>
+      </c>
       <c r="I19" s="5"/>
     </row>
     <row r="20" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1491,7 +1498,9 @@
       <c r="G20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H20" s="11"/>
+      <c r="H20" s="13" t="s">
+        <v>156</v>
+      </c>
       <c r="I20" s="3"/>
     </row>
     <row r="21" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1516,7 +1525,9 @@
       <c r="G21" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="10"/>
+      <c r="H21" s="13" t="s">
+        <v>156</v>
+      </c>
       <c r="I21" s="5"/>
     </row>
     <row r="22" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1541,7 +1552,9 @@
       <c r="G22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="11"/>
+      <c r="H22" s="13" t="s">
+        <v>156</v>
+      </c>
       <c r="I22" s="3"/>
     </row>
     <row r="23" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1566,7 +1579,9 @@
       <c r="G23" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H23" s="10"/>
+      <c r="H23" s="13" t="s">
+        <v>156</v>
+      </c>
       <c r="I23" s="5"/>
     </row>
     <row r="24" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1591,7 +1606,9 @@
       <c r="G24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="11"/>
+      <c r="H24" s="13" t="s">
+        <v>156</v>
+      </c>
       <c r="I24" s="3"/>
     </row>
     <row r="25" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1616,7 +1633,9 @@
       <c r="G25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H25" s="10"/>
+      <c r="H25" s="16" t="s">
+        <v>156</v>
+      </c>
       <c r="I25" s="5"/>
     </row>
     <row r="26" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1641,7 +1660,9 @@
       <c r="G26" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H26" s="11"/>
+      <c r="H26" s="16" t="s">
+        <v>156</v>
+      </c>
       <c r="I26" s="3"/>
     </row>
   </sheetData>

--- a/Vplan_TestCase_Checklist.xlsx
+++ b/Vplan_TestCase_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83377f57b735e897/Máy tính/AXI2AHB1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D43DF1A-4BDD-4587-B4B1-9169136FAD74}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EDE96F8-EA0B-4138-92E3-C8512CC88893}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="158">
   <si>
     <t>AXI4-to-AHB-Lite Bridge - Verification Test Cases</t>
   </si>
@@ -663,7 +663,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -691,9 +691,6 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -702,9 +699,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -979,28 +973,28 @@
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="2" max="2" width="44.88671875" customWidth="1"/>
     <col min="3" max="3" width="48" customWidth="1"/>
     <col min="4" max="4" width="50" customWidth="1"/>
     <col min="5" max="5" width="46" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="10" style="12" customWidth="1"/>
+    <col min="8" max="8" width="10" style="11" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1080,7 +1074,7 @@
       <c r="G4" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="12" t="s">
         <v>156</v>
       </c>
       <c r="I4" s="3"/>
@@ -1107,7 +1101,7 @@
       <c r="G5" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="13" t="s">
         <v>156</v>
       </c>
       <c r="I5" s="5"/>
@@ -1134,7 +1128,7 @@
       <c r="G6" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="13" t="s">
         <v>156</v>
       </c>
       <c r="I6" s="5"/>
@@ -1161,7 +1155,7 @@
       <c r="G7" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="12" t="s">
         <v>156</v>
       </c>
       <c r="I7" s="3"/>
@@ -1211,9 +1205,11 @@
         <v>46240</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="11"/>
+        <v>154</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>156</v>
+      </c>
       <c r="I9" s="3"/>
     </row>
     <row r="10" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
@@ -1261,9 +1257,11 @@
         <v>46240</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="11"/>
+        <v>154</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>156</v>
+      </c>
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1286,9 +1284,11 @@
         <v>46240</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="10"/>
+        <v>154</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>156</v>
+      </c>
       <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1311,9 +1311,11 @@
         <v>46240</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="11"/>
+        <v>154</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>156</v>
+      </c>
       <c r="I13" s="3"/>
     </row>
     <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1338,7 +1340,7 @@
       <c r="G14" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="H14" s="13" t="s">
         <v>156</v>
       </c>
       <c r="I14" s="3"/>
@@ -1365,7 +1367,7 @@
       <c r="G15" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="13" t="s">
         <v>156</v>
       </c>
       <c r="I15" s="5"/>
@@ -1392,7 +1394,7 @@
       <c r="G16" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="H16" s="13" t="s">
+      <c r="H16" s="12" t="s">
         <v>156</v>
       </c>
       <c r="I16" s="3"/>
@@ -1442,9 +1444,9 @@
         <v>46240</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H18" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H18" s="12" t="s">
         <v>156</v>
       </c>
       <c r="I18" s="3"/>
@@ -1469,9 +1471,9 @@
         <v>46240</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H19" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H19" s="12" t="s">
         <v>156</v>
       </c>
       <c r="I19" s="5"/>
@@ -1496,9 +1498,9 @@
         <v>46240</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H20" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H20" s="12" t="s">
         <v>156</v>
       </c>
       <c r="I20" s="3"/>
@@ -1523,9 +1525,9 @@
         <v>46240</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H21" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H21" s="12" t="s">
         <v>156</v>
       </c>
       <c r="I21" s="5"/>
@@ -1550,9 +1552,9 @@
         <v>46240</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H22" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H22" s="12" t="s">
         <v>156</v>
       </c>
       <c r="I22" s="3"/>
@@ -1577,9 +1579,9 @@
         <v>46240</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H23" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H23" s="12" t="s">
         <v>156</v>
       </c>
       <c r="I23" s="5"/>
@@ -1604,9 +1606,9 @@
         <v>46240</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H24" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H24" s="12" t="s">
         <v>156</v>
       </c>
       <c r="I24" s="3"/>
@@ -1631,9 +1633,9 @@
         <v>46240</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H25" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="H25" s="12" t="s">
         <v>156</v>
       </c>
       <c r="I25" s="5"/>
@@ -1658,9 +1660,9 @@
         <v>46240</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H26" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="H26" s="12" t="s">
         <v>156</v>
       </c>
       <c r="I26" s="3"/>
@@ -1702,17 +1704,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">

--- a/Vplan_TestCase_Checklist.xlsx
+++ b/Vplan_TestCase_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83377f57b735e897/Máy tính/AXI2AHB1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EDE96F8-EA0B-4138-92E3-C8512CC88893}"/>
+  <xr:revisionPtr revIDLastSave="185" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DD50E51-B9CC-4917-94C9-A470C50D12AC}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Checklist!$A$2:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Testcases!$A$2:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Testcases!$A$2:$I$25</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="191">
   <si>
     <t>AXI4-to-AHB-Lite Bridge - Verification Test Cases</t>
   </si>
@@ -238,18 +238,6 @@
     <t>AWBURST(=FIXED), AWLEN, WDATA, ARBURST(=FIXED), RDATA / HADDR(constant), HTRANS(NONSEQ)</t>
   </si>
   <si>
-    <t>axi4_blocking_cross_write_read_test</t>
-  </si>
-  <si>
-    <t>Cross write/read where read targets data written by a prior transaction.</t>
-  </si>
-  <si>
-    <t>Verify data coherency across separate write and read transactions routed through the bridge.</t>
-  </si>
-  <si>
-    <t>AWADDR, WDATA, ARADDR, RDATA / HADDR, HWDATA, HRDATA</t>
-  </si>
-  <si>
     <t>axi4_blocking_8b_write_read_test</t>
   </si>
   <si>
@@ -512,6 +500,117 @@
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>axi4_blocking_1kb_cross_incr_read_test</t>
+  </si>
+  <si>
+    <t>INCR burst read whose address range crosses a 1 KB boundary.</t>
+  </si>
+  <si>
+    <t>Verify the bridge splits the AXI4 read into two AHB-Lite INCR bursts of undefined length when a 1 KB boundary is crossed (per spec).</t>
+  </si>
+  <si>
+    <t>ARADDR, ARLEN, ARBURST(=INCR), RDATA, RLAST / HADDR, HBURST(=INCR undefined), HTRANS(restart)</t>
+  </si>
+  <si>
+    <t>axi4_blocking_1kb_cross_incr_write_test</t>
+  </si>
+  <si>
+    <t>INCR burst write whose address range crosses a 1 KB boundary.</t>
+  </si>
+  <si>
+    <t>Verify the bridge splits the AXI4 write into two AHB-Lite INCR bursts of undefined length when a 1 KB boundary is crossed.</t>
+  </si>
+  <si>
+    <t>AWADDR, AWLEN, AWBURST(=INCR), WDATA, WLAST / HADDR, HBURST(=INCR undefined), HTRANS(restart)</t>
+  </si>
+  <si>
+    <t>axi4_blocking_read_timeout_test</t>
+  </si>
+  <si>
+    <t>Read transaction where the AHB-Lite slave never responds, triggering bridge timeout.</t>
+  </si>
+  <si>
+    <t>Verify timeout logic waits the parameterized number of clocks, completes the AXI4 read with SLVERR, and drives IDLE on AHB-Lite (Fig 3-14).</t>
+  </si>
+  <si>
+    <t>ARVALID, RRESP(=SLVERR), RVALID / HTRANS(=IDLE), HREADY(stuck)</t>
+  </si>
+  <si>
+    <t>axi4_blocking_write_timeout_test</t>
+  </si>
+  <si>
+    <t>Write transaction where the AHB-Lite slave never responds, triggering bridge timeout.</t>
+  </si>
+  <si>
+    <t>Verify timeout logic completes the AXI4 write with SLVERR and drives IDLE on AHB-Lite (Fig 3-15).</t>
+  </si>
+  <si>
+    <t>AWVALID, WVALID, BRESP(=SLVERR), BVALID / HTRANS(=IDLE), HREADY(stuck)</t>
+  </si>
+  <si>
+    <t>axi4_blocking_read_write_priority_test</t>
+  </si>
+  <si>
+    <t>Simultaneous read and write request issued on the AXI4 interface in the same cycle.</t>
+  </si>
+  <si>
+    <t>Verify the bridge gives the read request higher priority and issues read before write on AHB-Lite (Fig 3-3).</t>
+  </si>
+  <si>
+    <t>ARVALID, AWVALID, WVALID, ARREADY, AWREADY / HADDR, HWRITE, HTRANS ordering</t>
+  </si>
+  <si>
+    <t>axi4_blocking_hprot_privileged_data_test</t>
+  </si>
+  <si>
+    <t>Transaction with privileged + data AWPROT/ARPROT and non-cacheable AWCACHE.</t>
+  </si>
+  <si>
+    <t>Verify AXI4 protection/cache attributes map to the correct m_ahb_hprot value (privileged, data, non-cacheable, non-bufferable) per Table 3-1.</t>
+  </si>
+  <si>
+    <t>AWPROT, ARPROT, AWCACHE, ARCACHE / HPROT[3:0]</t>
+  </si>
+  <si>
+    <t>axi4_blocking_hprot_instruction_bufferable_test</t>
+  </si>
+  <si>
+    <t>Transaction with instruction-access PROT and bufferable CACHE encoding.</t>
+  </si>
+  <si>
+    <t>Verify instruction access maps to opcode-fetch on AHB and bufferable maps to the corresponding HPROT bit per Table 3-1.</t>
+  </si>
+  <si>
+    <t>AWPROT(instr), AWCACHE(bufferable) / HPROT[3:0] (opcode + bufferable bits)</t>
+  </si>
+  <si>
+    <t>axi4_blocking_reset_test</t>
+  </si>
+  <si>
+    <t>Assert s_axi_aresetn during idle and during an active transaction.</t>
+  </si>
+  <si>
+    <t>Verify synchronous reset returns AXI4 and AHB-Lite outputs to their initial states and no transaction completes after reset assertion.</t>
+  </si>
+  <si>
+    <t>ARESETN / all AHB-Lite outputs return to initial (HTRANS=IDLE, HADDR=0, HPROT=0011)</t>
+  </si>
+  <si>
+    <t>axi4_blocking_back_to_back_write_read_test</t>
+  </si>
+  <si>
+    <t>Multiple back-to-back single write/read transactions with no idle gap.</t>
+  </si>
+  <si>
+    <t>Verify the bridge sustains continuous transactions and AHB HTRANS sequencing (NONSEQ/IDLE) is correct between them; checks 3-clk write / 4-clk read latency.</t>
+  </si>
+  <si>
+    <t>AWVALID/WVALID/ARVALID streams / HTRANS(NONSEQ-&gt;IDLE), HREADY</t>
+  </si>
+  <si>
+    <t>In Progress</t>
   </si>
 </sst>
 </file>
@@ -580,7 +679,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -608,18 +707,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
-        <bgColor rgb="FF003366"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
-        <bgColor rgb="FFCCFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -631,12 +718,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FFCCFFFF"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -659,11 +746,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -682,22 +797,44 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -969,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -979,711 +1116,911 @@
     <col min="5" max="5" width="46" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="10" style="11" customWidth="1"/>
+    <col min="8" max="8" width="10" style="8" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+      <c r="A3" s="11">
+        <v>1</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="I3" s="12"/>
+    </row>
+    <row r="4" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="15">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I4" s="16"/>
+    </row>
+    <row r="5" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="11">
+        <v>3</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I5" s="12"/>
+    </row>
+    <row r="6" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
+        <v>4</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I6" s="12"/>
+    </row>
+    <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="15">
+        <v>5</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I7" s="16"/>
+    </row>
+    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="11">
+        <v>6</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="14"/>
+      <c r="I8" s="12"/>
+    </row>
+    <row r="9" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="15">
+        <v>7</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I9" s="16"/>
+    </row>
+    <row r="10" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="11">
+        <v>8</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="14"/>
+      <c r="I10" s="12"/>
+    </row>
+    <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="15">
+        <v>9</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I11" s="16"/>
+    </row>
+    <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="11">
+        <v>10</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I12" s="12"/>
+    </row>
+    <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="15">
         <v>11</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="B13" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I13" s="16"/>
+    </row>
+    <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="15">
         <v>12</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="B14" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I14" s="16"/>
+    </row>
+    <row r="15" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="11">
         <v>13</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="B15" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I15" s="12"/>
+    </row>
+    <row r="16" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="15">
         <v>14</v>
       </c>
-      <c r="F3" s="8">
+      <c r="B16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="13">
         <v>46240</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G16" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I16" s="16"/>
+    </row>
+    <row r="17" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="15">
+        <v>15</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I17" s="16"/>
+    </row>
+    <row r="18" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="11">
+        <v>16</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I18" s="12"/>
+    </row>
+    <row r="19" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="15">
+        <v>17</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I19" s="16"/>
+    </row>
+    <row r="20" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="11">
+        <v>18</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I20" s="12"/>
+    </row>
+    <row r="21" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="15">
+        <v>19</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="H21" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I21" s="16"/>
+    </row>
+    <row r="22" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="11">
+        <v>20</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="F22" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="H22" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I22" s="12"/>
+    </row>
+    <row r="23" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="15">
+        <v>21</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="H23" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I23" s="16"/>
+    </row>
+    <row r="24" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="11">
+        <v>22</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F24" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="H24" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I24" s="12"/>
+    </row>
+    <row r="25" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="15">
+        <v>23</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F25" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="H25" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I25" s="16"/>
+    </row>
+    <row r="26" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="18">
+        <v>24</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="F26" s="13">
+        <v>46301</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="H26" s="23"/>
+      <c r="I26" s="21"/>
+    </row>
+    <row r="27" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="15">
+        <v>25</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="F27" s="13">
+        <v>46301</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="H27" s="23"/>
+      <c r="I27" s="22"/>
+    </row>
+    <row r="28" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="18">
+        <v>26</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="F28" s="13">
+        <v>46301</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="H28" s="23"/>
+      <c r="I28" s="21"/>
+    </row>
+    <row r="29" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="15">
+        <v>27</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="F29" s="13">
+        <v>46301</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="H29" s="23"/>
+      <c r="I29" s="22"/>
+    </row>
+    <row r="30" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="18">
+        <v>28</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30" s="13">
+        <v>46301</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="H30" s="20"/>
+      <c r="I30" s="21"/>
+    </row>
+    <row r="31" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="15">
+        <v>29</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="F31" s="13">
+        <v>46301</v>
+      </c>
+      <c r="G31" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="I3" s="5"/>
-    </row>
-    <row r="4" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>12</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>4</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="I6" s="5"/>
-    </row>
-    <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
-        <v>6</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="H31" s="23"/>
+      <c r="I31" s="22"/>
+    </row>
+    <row r="32" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="18">
+        <v>30</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32" s="13">
+        <v>46301</v>
+      </c>
+      <c r="G32" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="5"/>
-    </row>
-    <row r="9" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="H32" s="23"/>
+      <c r="I32" s="21"/>
+    </row>
+    <row r="33" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="15">
         <v>31</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="B33" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="F33" s="13">
+        <v>46301</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="23"/>
+      <c r="I33" s="22"/>
+    </row>
+    <row r="34" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="18">
         <v>32</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
-        <v>8</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="B34" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="F34" s="13">
+        <v>46301</v>
+      </c>
+      <c r="G34" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="5"/>
-    </row>
-    <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
-        <v>10</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I12" s="5"/>
-    </row>
-    <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>11</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I13" s="3"/>
-    </row>
-    <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="I14" s="3"/>
-    </row>
-    <row r="15" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="I15" s="5"/>
-    </row>
-    <row r="16" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F16" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>18</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H17" s="10"/>
-      <c r="I17" s="5"/>
-    </row>
-    <row r="18" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>19</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I18" s="3"/>
-    </row>
-    <row r="19" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
-        <v>20</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I19" s="5"/>
-    </row>
-    <row r="20" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>21</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F20" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I20" s="3"/>
-    </row>
-    <row r="21" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>22</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F21" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I21" s="5"/>
-    </row>
-    <row r="22" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
-        <v>23</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F22" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I22" s="3"/>
-    </row>
-    <row r="23" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="4">
-        <v>24</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="F23" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I23" s="5"/>
-    </row>
-    <row r="24" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>25</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F24" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I24" s="3"/>
-    </row>
-    <row r="25" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
-        <v>26</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F25" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I25" s="5"/>
-    </row>
-    <row r="26" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <v>27</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F26" s="8">
-        <v>46240</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H26" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I26" s="3"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="21"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:I25" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="G3:G26" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Not Started,In Progress,Completed,Blocked"</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="H3:H25" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"Pass,Fail,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H3:H26" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"Pass,Fail,N/A"</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="G3:G34" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"Not Started,In Progress,Completed,Blocked"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1704,36 +2041,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
+      <c r="A1" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>7</v>
@@ -1747,16 +2084,16 @@
     </row>
     <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -1768,16 +2105,16 @@
     </row>
     <row r="4" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>117</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -1789,16 +2126,16 @@
     </row>
     <row r="5" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -1810,16 +2147,16 @@
     </row>
     <row r="6" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -1831,16 +2168,16 @@
     </row>
     <row r="7" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -1852,13 +2189,13 @@
     </row>
     <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>62</v>
@@ -1873,16 +2210,16 @@
     </row>
     <row r="9" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -1894,16 +2231,16 @@
     </row>
     <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="D10" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -1915,13 +2252,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>30</v>
@@ -1936,13 +2273,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>26</v>
@@ -1957,16 +2294,16 @@
     </row>
     <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -1978,13 +2315,13 @@
     </row>
     <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>34</v>
@@ -1999,12 +2336,12 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C17" s="7">
         <f>COUNTA(A3:A14)</f>
@@ -2013,7 +2350,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C18" s="7">
         <f>COUNTIF(H3:H14,"Pass")</f>
@@ -2022,7 +2359,7 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C19" s="7">
         <f>COUNTIF(H3:H14,"Fail")</f>
@@ -2031,7 +2368,7 @@
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C20" s="7">
         <f>COUNTIF(G3:G14,"Completed")</f>

--- a/Vplan_TestCase_Checklist.xlsx
+++ b/Vplan_TestCase_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83377f57b735e897/Máy tính/AXI2AHB1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="185" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DD50E51-B9CC-4917-94C9-A470C50D12AC}"/>
+  <xr:revisionPtr revIDLastSave="187" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EA104FC-6EFD-4B78-9A71-6B2837CDEFF6}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="191">
   <si>
     <t>AXI4-to-AHB-Lite Bridge - Verification Test Cases</t>
   </si>
@@ -1801,7 +1801,9 @@
       <c r="G26" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="H26" s="23"/>
+      <c r="H26" s="17" t="s">
+        <v>152</v>
+      </c>
       <c r="I26" s="21"/>
     </row>
     <row r="27" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
@@ -1826,7 +1828,9 @@
       <c r="G27" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="H27" s="23"/>
+      <c r="H27" s="17" t="s">
+        <v>152</v>
+      </c>
       <c r="I27" s="22"/>
     </row>
     <row r="28" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
@@ -2010,7 +2014,7 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="H3:H25" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H3:H27" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Pass,Fail,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/Vplan_TestCase_Checklist.xlsx
+++ b/Vplan_TestCase_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83377f57b735e897/Máy tính/AXI2AHB1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="187" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EA104FC-6EFD-4B78-9A71-6B2837CDEFF6}"/>
+  <xr:revisionPtr revIDLastSave="193" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6144F89C-4DB1-4022-A3FB-A802E46269D6}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="191">
   <si>
     <t>AXI4-to-AHB-Lite Bridge - Verification Test Cases</t>
   </si>
@@ -1106,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1855,7 +1855,9 @@
       <c r="G28" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="H28" s="23"/>
+      <c r="H28" s="17" t="s">
+        <v>152</v>
+      </c>
       <c r="I28" s="21"/>
     </row>
     <row r="29" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1880,7 +1882,9 @@
       <c r="G29" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="H29" s="23"/>
+      <c r="H29" s="17" t="s">
+        <v>152</v>
+      </c>
       <c r="I29" s="22"/>
     </row>
     <row r="30" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -1909,77 +1913,65 @@
       <c r="I30" s="21"/>
     </row>
     <row r="31" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="15">
-        <v>29</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>181</v>
+      <c r="A31" s="18">
+        <v>30</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>185</v>
       </c>
       <c r="F31" s="13">
         <v>46301</v>
       </c>
-      <c r="G31" s="15" t="s">
+      <c r="G31" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="H31" s="23"/>
-      <c r="I31" s="22"/>
+      <c r="H31" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I31" s="21"/>
     </row>
     <row r="32" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="18">
-        <v>30</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>185</v>
+      <c r="A32" s="15">
+        <v>31</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>189</v>
       </c>
       <c r="F32" s="13">
         <v>46301</v>
       </c>
-      <c r="G32" s="18" t="s">
+      <c r="G32" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H32" s="23"/>
-      <c r="I32" s="21"/>
-    </row>
-    <row r="33" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="15">
-        <v>31</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="F33" s="13">
-        <v>46301</v>
-      </c>
-      <c r="G33" s="15" t="s">
-        <v>10</v>
-      </c>
+      <c r="I32" s="22"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="15"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="15"/>
       <c r="H33" s="23"/>
       <c r="I33" s="22"/>
     </row>
@@ -2007,6 +1999,31 @@
       </c>
       <c r="H34" s="23"/>
       <c r="I34" s="21"/>
+    </row>
+    <row r="35" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="15">
+        <v>29</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="F35" s="13">
+        <v>46301</v>
+      </c>
+      <c r="G35" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="23"/>
+      <c r="I35" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:I25" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -2014,11 +2031,11 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="H3:H27" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H3:H29 H31" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Pass,Fail,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G3:G34" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G3:G30 G31:G35" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Not Started,In Progress,Completed,Blocked"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/Vplan_TestCase_Checklist.xlsx
+++ b/Vplan_TestCase_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83377f57b735e897/Máy tính/AXI2AHB1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="193" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6144F89C-4DB1-4022-A3FB-A802E46269D6}"/>
+  <xr:revisionPtr revIDLastSave="214" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E167903-1E88-4DA9-A1DA-8532E782E16F}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Checklist!$A$2:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Testcases!$A$2:$I$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Testcases!$A$2:$I$23</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="198">
   <si>
     <t>AXI4-to-AHB-Lite Bridge - Verification Test Cases</t>
   </si>
@@ -73,9 +73,6 @@
     <t>Not Started</t>
   </si>
   <si>
-    <t>axi4_blocking_write_read_rand_test</t>
-  </si>
-  <si>
     <t>Randomized blocking write/read with random addresses, lengths and data.</t>
   </si>
   <si>
@@ -85,18 +82,12 @@
     <t>AWADDR, AWLEN, WDATA, WSTRB, ARADDR, RDATA / HADDR, HBURST, HWDATA, HRDATA</t>
   </si>
   <si>
-    <t>axi4_blocking_wrap_burst_write_test</t>
-  </si>
-  <si>
     <t>Verify AXI4 WRAP burst writes are correctly unrolled into AHB-Lite single/INCR accesses with proper address wrapping.</t>
   </si>
   <si>
     <t>AWBURST(=WRAP), AWLEN, AWSIZE, WDATA, WLAST / HADDR, HBURST, HWRITE, HTRANS</t>
   </si>
   <si>
-    <t>axi4_blocking_wrap_burst_write_read_test</t>
-  </si>
-  <si>
     <t>Blocking WRAP burst write then read back.</t>
   </si>
   <si>
@@ -106,9 +97,6 @@
     <t>AWBURST(=WRAP), WDATA, ARBURST(=WRAP), RDATA / HADDR, HBURST, HRDATA</t>
   </si>
   <si>
-    <t>axi4_blocking_wrap_burst_read_test</t>
-  </si>
-  <si>
     <t>Blocking WRAP burst read transaction.</t>
   </si>
   <si>
@@ -154,9 +142,6 @@
     <t>AWVALID, AWREADY, ARVALID, ARREADY, BID, RID / HTRANS, HREADY, HADDR</t>
   </si>
   <si>
-    <t>axi4_blocking_okay_response_write_test</t>
-  </si>
-  <si>
     <t>Write transaction expected to complete with OKAY response.</t>
   </si>
   <si>
@@ -166,9 +151,6 @@
     <t>AWADDR, WDATA, BRESP(=OKAY) / HRESP(=OKAY), HREADY</t>
   </si>
   <si>
-    <t>axi4_blocking_okay_response_write_read_test</t>
-  </si>
-  <si>
     <t>Write then read both expected to return OKAY response.</t>
   </si>
   <si>
@@ -178,9 +160,6 @@
     <t>BRESP(=OKAY), RRESP(=OKAY) / HRESP(=OKAY), HREADY</t>
   </si>
   <si>
-    <t>axi4_blocking_okay_response_read_test</t>
-  </si>
-  <si>
     <t>Read transaction expected to complete with OKAY response.</t>
   </si>
   <si>
@@ -190,9 +169,6 @@
     <t>ARADDR, RDATA, RRESP(=OKAY) / HRESP(=OKAY), HRDATA, HREADY</t>
   </si>
   <si>
-    <t>axi4_blocking_incr_burst_write_test</t>
-  </si>
-  <si>
     <t>Blocking INCR burst write transaction.</t>
   </si>
   <si>
@@ -202,9 +178,6 @@
     <t>AWBURST(=INCR), AWLEN, WDATA, WLAST / HADDR(incrementing), HBURST(=INCR), HTRANS(SEQ/NONSEQ)</t>
   </si>
   <si>
-    <t>axi4_blocking_incr_burst_write_read_test</t>
-  </si>
-  <si>
     <t>Blocking INCR burst write then read back.</t>
   </si>
   <si>
@@ -214,9 +187,6 @@
     <t>AWBURST(=INCR), WDATA, ARBURST(=INCR), RDATA / HADDR, HBURST, HRDATA</t>
   </si>
   <si>
-    <t>axi4_blocking_incr_burst_read_test</t>
-  </si>
-  <si>
     <t>Blocking INCR burst read transaction.</t>
   </si>
   <si>
@@ -238,9 +208,6 @@
     <t>AWBURST(=FIXED), AWLEN, WDATA, ARBURST(=FIXED), RDATA / HADDR(constant), HTRANS(NONSEQ)</t>
   </si>
   <si>
-    <t>axi4_blocking_8b_write_read_test</t>
-  </si>
-  <si>
     <t>8-bit (byte) write followed by read.</t>
   </si>
   <si>
@@ -250,9 +217,6 @@
     <t>AWSIZE(=0), WSTRB, WDATA[7:0], RDATA[7:0] / HSIZE(=BYTE), HWDATA, HRDATA</t>
   </si>
   <si>
-    <t>axi4_blocking_8b_write_data_test</t>
-  </si>
-  <si>
     <t>8-bit write-only data path test.</t>
   </si>
   <si>
@@ -262,9 +226,6 @@
     <t>AWSIZE(=0), WSTRB, WDATA[7:0] / HSIZE(=BYTE), HWDATA</t>
   </si>
   <si>
-    <t>axi4_blocking_8b_data_read_test</t>
-  </si>
-  <si>
     <t>8-bit read-only data path test.</t>
   </si>
   <si>
@@ -274,9 +235,6 @@
     <t>ARSIZE(=0), RDATA[7:0] / HSIZE(=BYTE), HRDATA</t>
   </si>
   <si>
-    <t>axi4_blocking_32b_write_read_test</t>
-  </si>
-  <si>
     <t>32-bit (word) write followed by read.</t>
   </si>
   <si>
@@ -286,9 +244,6 @@
     <t>AWSIZE(=2), WSTRB, WDATA[31:0], RDATA[31:0] / HSIZE(=WORD), HWDATA, HRDATA</t>
   </si>
   <si>
-    <t>axi4_blocking_32b_write_data_test</t>
-  </si>
-  <si>
     <t>32-bit write-only data path test.</t>
   </si>
   <si>
@@ -298,9 +253,6 @@
     <t>AWSIZE(=2), WSTRB, WDATA[31:0] / HSIZE(=WORD), HWDATA</t>
   </si>
   <si>
-    <t>axi4_blocking_32b_data_read_test</t>
-  </si>
-  <si>
     <t>32-bit read-only data path test.</t>
   </si>
   <si>
@@ -310,9 +262,6 @@
     <t>ARSIZE(=2), RDATA[31:0] / HSIZE(=WORD), HRDATA</t>
   </si>
   <si>
-    <t>axi4_blocking_16b_write_read_test</t>
-  </si>
-  <si>
     <t>16-bit (halfword) write followed by read.</t>
   </si>
   <si>
@@ -322,9 +271,6 @@
     <t>AWSIZE(=1), WSTRB, WDATA[15:0], RDATA[15:0] / HSIZE(=HALFWORD), HWDATA, HRDATA</t>
   </si>
   <si>
-    <t>axi4_blocking_16b_write_data_test</t>
-  </si>
-  <si>
     <t>16-bit write-only data path test.</t>
   </si>
   <si>
@@ -334,9 +280,6 @@
     <t>AWSIZE(=1), WSTRB, WDATA[15:0] / HSIZE(=HALFWORD), HWDATA</t>
   </si>
   <si>
-    <t>axi4_blocking_16b_data_read_test</t>
-  </si>
-  <si>
     <t>16-bit read-only data path test.</t>
   </si>
   <si>
@@ -502,9 +445,6 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>axi4_blocking_1kb_cross_incr_read_test</t>
-  </si>
-  <si>
     <t>INCR burst read whose address range crosses a 1 KB boundary.</t>
   </si>
   <si>
@@ -514,9 +454,6 @@
     <t>ARADDR, ARLEN, ARBURST(=INCR), RDATA, RLAST / HADDR, HBURST(=INCR undefined), HTRANS(restart)</t>
   </si>
   <si>
-    <t>axi4_blocking_1kb_cross_incr_write_test</t>
-  </si>
-  <si>
     <t>INCR burst write whose address range crosses a 1 KB boundary.</t>
   </si>
   <si>
@@ -526,9 +463,6 @@
     <t>AWADDR, AWLEN, AWBURST(=INCR), WDATA, WLAST / HADDR, HBURST(=INCR undefined), HTRANS(restart)</t>
   </si>
   <si>
-    <t>axi4_blocking_read_timeout_test</t>
-  </si>
-  <si>
     <t>Read transaction where the AHB-Lite slave never responds, triggering bridge timeout.</t>
   </si>
   <si>
@@ -538,9 +472,6 @@
     <t>ARVALID, RRESP(=SLVERR), RVALID / HTRANS(=IDLE), HREADY(stuck)</t>
   </si>
   <si>
-    <t>axi4_blocking_write_timeout_test</t>
-  </si>
-  <si>
     <t>Write transaction where the AHB-Lite slave never responds, triggering bridge timeout.</t>
   </si>
   <si>
@@ -550,9 +481,6 @@
     <t>AWVALID, WVALID, BRESP(=SLVERR), BVALID / HTRANS(=IDLE), HREADY(stuck)</t>
   </si>
   <si>
-    <t>axi4_blocking_read_write_priority_test</t>
-  </si>
-  <si>
     <t>Simultaneous read and write request issued on the AXI4 interface in the same cycle.</t>
   </si>
   <si>
@@ -562,9 +490,6 @@
     <t>ARVALID, AWVALID, WVALID, ARREADY, AWREADY / HADDR, HWRITE, HTRANS ordering</t>
   </si>
   <si>
-    <t>axi4_blocking_hprot_privileged_data_test</t>
-  </si>
-  <si>
     <t>Transaction with privileged + data AWPROT/ARPROT and non-cacheable AWCACHE.</t>
   </si>
   <si>
@@ -574,9 +499,6 @@
     <t>AWPROT, ARPROT, AWCACHE, ARCACHE / HPROT[3:0]</t>
   </si>
   <si>
-    <t>axi4_blocking_hprot_instruction_bufferable_test</t>
-  </si>
-  <si>
     <t>Transaction with instruction-access PROT and bufferable CACHE encoding.</t>
   </si>
   <si>
@@ -586,9 +508,6 @@
     <t>AWPROT(instr), AWCACHE(bufferable) / HPROT[3:0] (opcode + bufferable bits)</t>
   </si>
   <si>
-    <t>axi4_blocking_reset_test</t>
-  </si>
-  <si>
     <t>Assert s_axi_aresetn during idle and during an active transaction.</t>
   </si>
   <si>
@@ -598,9 +517,6 @@
     <t>ARESETN / all AHB-Lite outputs return to initial (HTRANS=IDLE, HADDR=0, HPROT=0011)</t>
   </si>
   <si>
-    <t>axi4_blocking_back_to_back_write_read_test</t>
-  </si>
-  <si>
     <t>Multiple back-to-back single write/read transactions with no idle gap.</t>
   </si>
   <si>
@@ -611,6 +527,111 @@
   </si>
   <si>
     <t>In Progress</t>
+  </si>
+  <si>
+    <t>x2h_blocking_unaligned_addr_read_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_write_read_rand_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_wrap_burst_write_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_incr_burst_write_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_wrap_burst_write_read_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_wrap_burst_read_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_slave_error_write_read_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_okay_response_write_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_okay_response_write_read_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_okay_response_read_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_incr_burst_write_read_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_incr_burst_read_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_fixed_burst_write_read_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_8b_write_read_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_8b_write_data_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_8b_data_read_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_32b_write_read_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_32b_write_data_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_32b_data_read_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_16b_write_read_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_16b_write_data_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_16b_data_read_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_1kb_cross_incr_read_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_1kb_cross_incr_write_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_read_timeout_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_write_timeout_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_read_write_priority_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_reset_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_back_to_back_write_read_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_hprot_privileged_data_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_hprot_instruction_bufferable_test</t>
+  </si>
+  <si>
+    <t>x2h_blocking_outstanding_transfer_write_read_test</t>
+  </si>
+  <si>
+    <t>x2h_virtual_bk_narrow_unaligned_sparse_seq</t>
+  </si>
+  <si>
+    <t>Verify the bridge analysis narrow transfer with no sparse/hole and unalign.</t>
+  </si>
+  <si>
+    <t>Bridge monitor strb and size to convert ahb_size</t>
   </si>
 </sst>
 </file>
@@ -778,7 +799,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -831,7 +852,6 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1121,17 +1141,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
@@ -1167,16 +1187,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>13</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>14</v>
       </c>
       <c r="F3" s="13">
         <v>46240</v>
@@ -1185,7 +1205,7 @@
         <v>10</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="I3" s="12"/>
     </row>
@@ -1194,25 +1214,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="16" t="s">
         <v>15</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>17</v>
       </c>
       <c r="F4" s="13">
         <v>46240</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="I4" s="16"/>
     </row>
@@ -1221,25 +1241,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>50</v>
+        <v>166</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F5" s="13">
         <v>46240</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="I5" s="12"/>
     </row>
@@ -1248,25 +1268,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>18</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>21</v>
       </c>
       <c r="F6" s="13">
         <v>46240</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="I6" s="12"/>
     </row>
@@ -1275,767 +1295,779 @@
         <v>5</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F7" s="13">
         <v>46240</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="I7" s="16"/>
     </row>
     <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="11">
-        <v>6</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="12" t="s">
+      <c r="A8" s="15">
+        <v>7</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="16" t="s">
         <v>29</v>
       </c>
       <c r="F8" s="13">
         <v>46240</v>
       </c>
-      <c r="G8" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="12"/>
+      <c r="G8" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="I8" s="16"/>
     </row>
     <row r="9" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>30</v>
+        <v>170</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F9" s="13">
         <v>46240</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="I9" s="16"/>
     </row>
-    <row r="10" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>34</v>
+        <v>171</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F10" s="13">
         <v>46240</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="14"/>
+        <v>131</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>133</v>
+      </c>
       <c r="I10" s="12"/>
     </row>
     <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>38</v>
+        <v>172</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F11" s="13">
         <v>46240</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="I11" s="16"/>
     </row>
     <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="11">
-        <v>10</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>45</v>
+      <c r="A12" s="15">
+        <v>12</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="F12" s="13">
         <v>46240</v>
       </c>
-      <c r="G12" s="11" t="s">
-        <v>150</v>
+      <c r="G12" s="15" t="s">
+        <v>131</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="I12" s="12"/>
+        <v>133</v>
+      </c>
+      <c r="I12" s="16"/>
     </row>
     <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="15">
-        <v>11</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="16" t="s">
+      <c r="A13" s="11">
+        <v>13</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>49</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>51</v>
       </c>
       <c r="F13" s="13">
         <v>46240</v>
       </c>
-      <c r="G13" s="15" t="s">
-        <v>150</v>
+      <c r="G13" s="11" t="s">
+        <v>131</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="I13" s="16"/>
-    </row>
-    <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="I13" s="12"/>
+    </row>
+    <row r="14" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A14" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B14" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="E14" s="16" t="s">
         <v>55</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>57</v>
       </c>
       <c r="F14" s="13">
         <v>46240</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="I14" s="16"/>
     </row>
     <row r="15" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="11">
-        <v>13</v>
-      </c>
-      <c r="B15" s="12" t="s">
+      <c r="A15" s="15">
+        <v>15</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="16" t="s">
         <v>58</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>61</v>
       </c>
       <c r="F15" s="13">
         <v>46240</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>150</v>
+      <c r="G15" s="15" t="s">
+        <v>131</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="I15" s="12"/>
-    </row>
-    <row r="16" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="15">
-        <v>14</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>65</v>
+        <v>133</v>
+      </c>
+      <c r="I15" s="16"/>
+    </row>
+    <row r="16" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="11">
+        <v>16</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="F16" s="13">
         <v>46240</v>
       </c>
-      <c r="G16" s="15" t="s">
-        <v>150</v>
+      <c r="G16" s="11" t="s">
+        <v>131</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="I16" s="16"/>
+        <v>133</v>
+      </c>
+      <c r="I16" s="12"/>
     </row>
     <row r="17" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>66</v>
+        <v>178</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F17" s="13">
         <v>46240</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="I17" s="16"/>
     </row>
     <row r="18" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>70</v>
+        <v>179</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F18" s="13">
         <v>46240</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="I18" s="12"/>
     </row>
     <row r="19" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A19" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F19" s="13">
         <v>46240</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="I19" s="16"/>
     </row>
     <row r="20" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F20" s="13">
         <v>46240</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="I20" s="12"/>
     </row>
     <row r="21" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A21" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F21" s="13">
         <v>46240</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="I21" s="16"/>
     </row>
     <row r="22" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>86</v>
+        <v>183</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F22" s="13">
         <v>46240</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="I22" s="12"/>
     </row>
     <row r="23" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A23" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>90</v>
+        <v>184</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="F23" s="13">
         <v>46240</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="I23" s="16"/>
     </row>
-    <row r="24" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="11">
-        <v>22</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>97</v>
+    <row r="24" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="18">
+        <v>24</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>137</v>
       </c>
       <c r="F24" s="13">
-        <v>46240</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>150</v>
+        <v>46301</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>162</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="I24" s="12"/>
-    </row>
-    <row r="25" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="I24" s="20"/>
+    </row>
+    <row r="25" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A25" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>98</v>
+        <v>186</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="F25" s="13">
-        <v>46240</v>
+        <v>46301</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="I25" s="16"/>
+        <v>133</v>
+      </c>
+      <c r="I25" s="21"/>
     </row>
     <row r="26" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A26" s="18">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="F26" s="13">
         <v>46301</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="I26" s="21"/>
-    </row>
-    <row r="27" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="I26" s="20"/>
+    </row>
+    <row r="27" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A27" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="F27" s="13">
         <v>46301</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="I27" s="22"/>
-    </row>
-    <row r="28" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="I27" s="21"/>
+    </row>
+    <row r="28" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A28" s="18">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="F28" s="13">
         <v>46301</v>
       </c>
       <c r="G28" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="H28" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="I28" s="20"/>
+    </row>
+    <row r="29" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="18">
+        <v>30</v>
+      </c>
+      <c r="B29" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="H28" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="I28" s="21"/>
-    </row>
-    <row r="29" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="15">
-        <v>27</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>169</v>
+      <c r="C29" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>158</v>
       </c>
       <c r="F29" s="13">
         <v>46301</v>
       </c>
-      <c r="G29" s="15" t="s">
-        <v>190</v>
+      <c r="G29" s="18" t="s">
+        <v>10</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="I29" s="22"/>
-    </row>
-    <row r="30" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="18">
-        <v>28</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>173</v>
+        <v>133</v>
+      </c>
+      <c r="I29" s="20"/>
+    </row>
+    <row r="30" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="15">
+        <v>31</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>161</v>
       </c>
       <c r="F30" s="13">
         <v>46301</v>
       </c>
-      <c r="G30" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="H30" s="20"/>
+      <c r="G30" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" s="22"/>
       <c r="I30" s="21"/>
     </row>
-    <row r="31" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="18">
-        <v>30</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="F31" s="13">
+    <row r="31" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="15"/>
+      <c r="B31" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="13"/>
+      <c r="G31" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" s="22"/>
+      <c r="I31" s="21"/>
+    </row>
+    <row r="32" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="11">
+        <v>6</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="14"/>
+      <c r="I32" s="12"/>
+    </row>
+    <row r="33" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="18">
+        <v>32</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="F33" s="13">
         <v>46301</v>
       </c>
-      <c r="G31" s="18" t="s">
+      <c r="G33" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="H31" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="I31" s="21"/>
-    </row>
-    <row r="32" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="15">
-        <v>31</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="F32" s="13">
-        <v>46301</v>
-      </c>
-      <c r="G32" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H32" s="23"/>
-      <c r="I32" s="22"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="15"/>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="20"/>
     </row>
     <row r="34" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="18">
-        <v>32</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="C34" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>177</v>
+      <c r="A34" s="15">
+        <v>29</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>155</v>
       </c>
       <c r="F34" s="13">
         <v>46301</v>
       </c>
-      <c r="G34" s="18" t="s">
+      <c r="G34" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H34" s="23"/>
+      <c r="H34" s="22"/>
       <c r="I34" s="21"/>
     </row>
     <row r="35" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="15">
-        <v>29</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="E35" s="16" t="s">
-        <v>181</v>
+      <c r="A35" s="11">
+        <v>8</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="F35" s="13">
-        <v>46301</v>
-      </c>
-      <c r="G35" s="15" t="s">
+        <v>46240</v>
+      </c>
+      <c r="G35" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H35" s="23"/>
-      <c r="I35" s="22"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I25" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:I23" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="H3:H29 H31" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H32 H3:H8 H35 H9:H29" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Pass,Fail,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G3:G30 G31:G35" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G3:G35" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Not Started,In Progress,Completed,Blocked"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2062,36 +2094,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
+      <c r="A1" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>7</v>
@@ -2105,16 +2137,16 @@
     </row>
     <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -2126,16 +2158,16 @@
     </row>
     <row r="4" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -2147,16 +2179,16 @@
     </row>
     <row r="5" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -2168,16 +2200,16 @@
     </row>
     <row r="6" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -2189,16 +2221,16 @@
     </row>
     <row r="7" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -2210,16 +2242,16 @@
     </row>
     <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
@@ -2231,16 +2263,16 @@
     </row>
     <row r="9" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -2252,16 +2284,16 @@
     </row>
     <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -2273,16 +2305,16 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -2294,16 +2326,16 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -2315,16 +2347,16 @@
     </row>
     <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -2336,16 +2368,16 @@
     </row>
     <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -2357,12 +2389,12 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C17" s="7">
         <f>COUNTA(A3:A14)</f>
@@ -2371,7 +2403,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C18" s="7">
         <f>COUNTIF(H3:H14,"Pass")</f>
@@ -2380,7 +2412,7 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C19" s="7">
         <f>COUNTIF(H3:H14,"Fail")</f>
@@ -2389,7 +2421,7 @@
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="C20" s="7">
         <f>COUNTIF(G3:G14,"Completed")</f>

--- a/Vplan_TestCase_Checklist.xlsx
+++ b/Vplan_TestCase_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83377f57b735e897/Máy tính/AXI2AHB1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="214" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E167903-1E88-4DA9-A1DA-8532E782E16F}"/>
+  <xr:revisionPtr revIDLastSave="232" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A3D0436-EA0B-4411-9ED0-E47CE6EAEBEB}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Checklist!$A$2:$I$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Testcases!$A$2:$I$23</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="200">
   <si>
     <t>AXI4-to-AHB-Lite Bridge - Verification Test Cases</t>
   </si>
@@ -526,9 +526,6 @@
     <t>AWVALID/WVALID/ARVALID streams / HTRANS(NONSEQ-&gt;IDLE), HREADY</t>
   </si>
   <si>
-    <t>In Progress</t>
-  </si>
-  <si>
     <t>x2h_blocking_unaligned_addr_read_test</t>
   </si>
   <si>
@@ -632,6 +629,15 @@
   </si>
   <si>
     <t>Bridge monitor strb and size to convert ahb_size</t>
+  </si>
+  <si>
+    <t>x2h_blocking_illegal_axsize_slverr_test</t>
+  </si>
+  <si>
+    <t>Verify the bridge resolve size transfer &gt; data buswidth, .</t>
+  </si>
+  <si>
+    <t>slverr</t>
   </si>
 </sst>
 </file>
@@ -1126,7 +1132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1187,7 +1193,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>11</v>
@@ -1214,7 +1220,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C4" s="16" t="s">
         <v>132</v>
@@ -1241,7 +1247,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>43</v>
@@ -1268,7 +1274,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>16</v>
@@ -1295,7 +1301,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>19</v>
@@ -1322,7 +1328,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>27</v>
@@ -1349,7 +1355,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>34</v>
@@ -1376,7 +1382,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>37</v>
@@ -1403,7 +1409,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>40</v>
@@ -1430,7 +1436,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>46</v>
@@ -1457,7 +1463,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>49</v>
@@ -1484,7 +1490,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>53</v>
@@ -1511,7 +1517,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>56</v>
@@ -1538,7 +1544,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>59</v>
@@ -1565,7 +1571,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>62</v>
@@ -1592,7 +1598,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>65</v>
@@ -1619,7 +1625,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>68</v>
@@ -1646,7 +1652,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>71</v>
@@ -1673,7 +1679,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>74</v>
@@ -1700,7 +1706,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>77</v>
@@ -1727,7 +1733,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>80</v>
@@ -1754,7 +1760,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C24" s="19" t="s">
         <v>135</v>
@@ -1769,7 +1775,7 @@
         <v>46301</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>133</v>
@@ -1781,7 +1787,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>138</v>
@@ -1796,7 +1802,7 @@
         <v>46301</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>133</v>
@@ -1808,7 +1814,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>141</v>
@@ -1823,7 +1829,7 @@
         <v>46301</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>133</v>
@@ -1835,7 +1841,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>144</v>
@@ -1850,7 +1856,7 @@
         <v>46301</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>133</v>
@@ -1862,7 +1868,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C28" s="19" t="s">
         <v>147</v>
@@ -1877,7 +1883,7 @@
         <v>46301</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>133</v>
@@ -1889,7 +1895,7 @@
         <v>30</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C29" s="19" t="s">
         <v>156</v>
@@ -1904,7 +1910,7 @@
         <v>46301</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>133</v>
@@ -1916,7 +1922,7 @@
         <v>31</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>159</v>
@@ -1931,131 +1937,156 @@
         <v>46301</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H30" s="22"/>
+        <v>131</v>
+      </c>
+      <c r="H30" s="17" t="s">
+        <v>133</v>
+      </c>
       <c r="I30" s="21"/>
     </row>
     <row r="31" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A31" s="15"/>
       <c r="B31" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="C31" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="D31" s="16" t="s">
         <v>196</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>197</v>
       </c>
       <c r="E31" s="16" t="s">
         <v>13</v>
       </c>
       <c r="F31" s="13"/>
       <c r="G31" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="21"/>
+    </row>
+    <row r="32" spans="1:9" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="15"/>
+      <c r="B32" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="E32" s="16"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="I32" s="21"/>
+    </row>
+    <row r="33" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="11">
+        <v>6</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="13">
+        <v>46240</v>
+      </c>
+      <c r="G33" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H31" s="22"/>
-      <c r="I31" s="21"/>
-    </row>
-    <row r="32" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="11">
-        <v>6</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="13">
-        <v>46240</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H32" s="14"/>
-      <c r="I32" s="12"/>
-    </row>
-    <row r="33" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="18">
+      <c r="H33" s="14"/>
+      <c r="I33" s="12"/>
+    </row>
+    <row r="34" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="18">
         <v>32</v>
       </c>
-      <c r="B33" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="C33" s="19" t="s">
+      <c r="B34" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="C34" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D34" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="E33" s="19" t="s">
+      <c r="E34" s="19" t="s">
         <v>152</v>
-      </c>
-      <c r="F33" s="13">
-        <v>46301</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="H33" s="22"/>
-      <c r="I33" s="20"/>
-    </row>
-    <row r="34" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="15">
-        <v>29</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>155</v>
       </c>
       <c r="F34" s="13">
         <v>46301</v>
       </c>
-      <c r="G34" s="15" t="s">
+      <c r="G34" s="18" t="s">
         <v>10</v>
       </c>
       <c r="H34" s="22"/>
-      <c r="I34" s="21"/>
+      <c r="I34" s="20"/>
     </row>
     <row r="35" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="11">
+      <c r="A35" s="15">
+        <v>29</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="F35" s="13">
+        <v>46301</v>
+      </c>
+      <c r="G35" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="22"/>
+      <c r="I35" s="21"/>
+    </row>
+    <row r="36" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="11">
         <v>8</v>
       </c>
-      <c r="B35" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="C35" s="12" t="s">
+      <c r="B36" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C36" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D36" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="E36" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F36" s="13">
         <v>46240</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="G36" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H35" s="14"/>
-      <c r="I35" s="12"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:I23" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -2063,11 +2094,11 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="H32 H3:H8 H35 H9:H29" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H36 H3:H33" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Pass,Fail,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G3:G35" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G3:G36" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Not Started,In Progress,Completed,Blocked"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/Vplan_TestCase_Checklist.xlsx
+++ b/Vplan_TestCase_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83377f57b735e897/Máy tính/AXI2AHB1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A3D0436-EA0B-4411-9ED0-E47CE6EAEBEB}"/>
+  <xr:revisionPtr revIDLastSave="233" documentId="11_96BAEF71EA07F57B813C8FC1F4B3DE81EE829617" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61141E6E-79BD-4531-A579-E668EB33F104}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="200">
   <si>
     <t>AXI4-to-AHB-Lite Bridge - Verification Test Cases</t>
   </si>
@@ -2010,7 +2010,9 @@
       <c r="G33" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H33" s="14"/>
+      <c r="H33" s="17" t="s">
+        <v>133</v>
+      </c>
       <c r="I33" s="12"/>
     </row>
     <row r="34" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
